--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/06 Junio/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/07 Julio/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DFDD8B8-67E4-4572-8F38-46F75741B918}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B7DDD1-5034-46BF-8A28-C98FF2DBA3CC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="79">
   <si>
     <t>Año</t>
   </si>
@@ -255,6 +255,21 @@
   </si>
   <si>
     <t>78.0%</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>92.2%</t>
+  </si>
+  <si>
+    <t>108.0%</t>
+  </si>
+  <si>
+    <t>194.0%</t>
+  </si>
+  <si>
+    <t>152.0%</t>
   </si>
 </sst>
 </file>
@@ -264,7 +279,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,13 +291,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -317,21 +325,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -631,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -2850,7 +2855,7 @@
         <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
@@ -2862,13 +2867,13 @@
         <v>24</v>
       </c>
       <c r="F64">
+        <v>45</v>
+      </c>
+      <c r="G64">
+        <v>41.5</v>
+      </c>
+      <c r="H64" t="s">
         <v>75</v>
-      </c>
-      <c r="G64">
-        <v>75.5</v>
-      </c>
-      <c r="H64" t="s">
-        <v>63</v>
       </c>
       <c r="I64" t="s">
         <v>29</v>
@@ -2877,7 +2882,7 @@
         <v>17</v>
       </c>
       <c r="K64" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2885,7 +2890,7 @@
         <v>2026</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C65" t="s">
         <v>22</v>
@@ -2900,10 +2905,10 @@
         <v>150</v>
       </c>
       <c r="G65">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="H65" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I65" t="s">
         <v>29</v>
@@ -2912,7 +2917,7 @@
         <v>17</v>
       </c>
       <c r="K65" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2920,7 +2925,7 @@
         <v>2026</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
         <v>26</v>
@@ -2947,7 +2952,7 @@
         <v>17</v>
       </c>
       <c r="K66" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2955,7 +2960,7 @@
         <v>2026</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
@@ -2970,20 +2975,19 @@
         <v>100000</v>
       </c>
       <c r="G67">
-        <v>107085</v>
-      </c>
-      <c r="H67" s="3">
-        <f>G67/F67</f>
-        <v>1.0708500000000001</v>
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
       </c>
       <c r="I67" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J67" t="s">
         <v>17</v>
       </c>
       <c r="K67" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2991,7 +2995,7 @@
         <v>2026</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -3006,10 +3010,10 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I68" t="s">
         <v>29</v>
@@ -3018,7 +3022,7 @@
         <v>17</v>
       </c>
       <c r="K68" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -3026,7 +3030,7 @@
         <v>2026</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
@@ -3041,10 +3045,10 @@
         <v>50</v>
       </c>
       <c r="G69">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H69" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I69" t="s">
         <v>29</v>
@@ -3053,7 +3057,7 @@
         <v>17</v>
       </c>
       <c r="K69" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -3061,7 +3065,7 @@
         <v>2026</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -3070,16 +3074,16 @@
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F70">
         <v>25</v>
       </c>
       <c r="G70">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I70" t="s">
         <v>16</v>
@@ -3088,7 +3092,7 @@
         <v>17</v>
       </c>
       <c r="K70" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -3096,7 +3100,7 @@
         <v>2026</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
         <v>22</v>
@@ -3105,95 +3109,25 @@
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F71">
         <v>50</v>
       </c>
       <c r="G71">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="H71" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="I71" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
       </c>
       <c r="K71" s="2">
-        <v>46226.753580955083</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>2026</v>
-      </c>
-      <c r="B72" t="s">
-        <v>68</v>
-      </c>
-      <c r="C72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" t="s">
-        <v>20</v>
-      </c>
-      <c r="F72">
-        <v>25</v>
-      </c>
-      <c r="G72">
-        <v>17</v>
-      </c>
-      <c r="H72" t="s">
-        <v>41</v>
-      </c>
-      <c r="I72" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" t="s">
-        <v>17</v>
-      </c>
-      <c r="K72" s="2">
-        <v>46226.753580955083</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>2026</v>
-      </c>
-      <c r="B73" t="s">
-        <v>68</v>
-      </c>
-      <c r="C73" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" t="s">
-        <v>20</v>
-      </c>
-      <c r="F73">
-        <v>50</v>
-      </c>
-      <c r="G73">
-        <v>39</v>
-      </c>
-      <c r="H73" t="s">
-        <v>73</v>
-      </c>
-      <c r="I73" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" t="s">
-        <v>17</v>
-      </c>
-      <c r="K73" s="2">
-        <v>46226.753580955083</v>
+        <v>46255.761959169773</v>
       </c>
     </row>
   </sheetData>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/07 Julio/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/08 Agosto/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B7DDD1-5034-46BF-8A28-C98FF2DBA3CC}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE224B8-4484-4D30-92DF-D2631A2CE667}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="84">
   <si>
     <t>Año</t>
   </si>
@@ -83,18 +70,21 @@
     <t>110.0%</t>
   </si>
   <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>director</t>
+  </si>
+  <si>
+    <t>Raiza Lorena Urzola Lora</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
     <t>0%</t>
   </si>
   <si>
-    <t>director</t>
-  </si>
-  <si>
-    <t>Raiza Lorena Urzola Lora</t>
-  </si>
-  <si>
-    <t>5.0%</t>
-  </si>
-  <si>
     <t>Yessica Yulieth Moreno</t>
   </si>
   <si>
@@ -104,6 +94,15 @@
     <t>Referido - bono</t>
   </si>
   <si>
+    <t>157.5%</t>
+  </si>
+  <si>
+    <t>187.5%</t>
+  </si>
+  <si>
+    <t>117.5%</t>
+  </si>
+  <si>
     <t>Líder</t>
   </si>
   <si>
@@ -113,6 +112,12 @@
     <t>44.2%</t>
   </si>
   <si>
+    <t>92.5%</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
     <t>Pyme Móvil - salarial</t>
   </si>
   <si>
@@ -122,51 +127,33 @@
     <t>CLOUND - salarial</t>
   </si>
   <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>157.5%</t>
-  </si>
-  <si>
-    <t>187.5%</t>
-  </si>
-  <si>
-    <t>117.5%</t>
-  </si>
-  <si>
-    <t>92.5%</t>
-  </si>
-  <si>
-    <t>90%</t>
-  </si>
-  <si>
     <t>Febrero</t>
   </si>
   <si>
+    <t>96.0%</t>
+  </si>
+  <si>
+    <t>122.0%</t>
+  </si>
+  <si>
+    <t>68.0%</t>
+  </si>
+  <si>
+    <t>116.0%</t>
+  </si>
+  <si>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>104.0%</t>
+  </si>
+  <si>
+    <t>80.7%</t>
+  </si>
+  <si>
     <t>113.3%</t>
   </si>
   <si>
-    <t>80.7%</t>
-  </si>
-  <si>
-    <t>104.0%</t>
-  </si>
-  <si>
-    <t>52.0%</t>
-  </si>
-  <si>
-    <t>116.0%</t>
-  </si>
-  <si>
-    <t>68.0%</t>
-  </si>
-  <si>
-    <t>122.0%</t>
-  </si>
-  <si>
-    <t>96.0%</t>
-  </si>
-  <si>
     <t>Marzo</t>
   </si>
   <si>
@@ -270,6 +257,21 @@
   </si>
   <si>
     <t>152.0%</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>94.0%</t>
+  </si>
+  <si>
+    <t>92.0%</t>
+  </si>
+  <si>
+    <t>138.0%</t>
+  </si>
+  <si>
+    <t>136.0%</t>
   </si>
 </sst>
 </file>
@@ -277,7 +279,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -291,6 +293,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -333,7 +336,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,12 +639,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -706,7 +707,7 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -741,7 +742,7 @@
         <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -764,7 +765,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -773,10 +774,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -793,7 +794,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -808,10 +809,10 @@
         <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -828,7 +829,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -843,10 +844,10 @@
         <v>75</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -863,13 +864,13 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>40</v>
@@ -878,10 +879,10 @@
         <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -901,10 +902,10 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>60</v>
@@ -913,10 +914,10 @@
         <v>26.5</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -933,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>200</v>
@@ -948,10 +949,10 @@
         <v>185</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -968,13 +969,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -983,10 +984,10 @@
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -1003,13 +1004,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
         <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1018,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -1053,16 +1054,16 @@
         <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1073,7 +1074,7 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1088,16 +1089,16 @@
         <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1123,16 +1124,16 @@
         <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
       </c>
       <c r="K14" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1143,7 +1144,7 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1158,16 +1159,16 @@
         <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1184,7 +1185,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16">
         <v>25</v>
@@ -1193,16 +1194,16 @@
         <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
       <c r="K16" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1213,13 +1214,13 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -1228,16 +1229,16 @@
         <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
       </c>
       <c r="K17" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1251,10 +1252,10 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>75</v>
@@ -1263,16 +1264,16 @@
         <v>60.5</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1283,13 +1284,13 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19">
         <v>150</v>
@@ -1298,16 +1299,16 @@
         <v>170</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
       </c>
       <c r="K19" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1318,13 +1319,13 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F20">
         <v>60</v>
@@ -1333,16 +1334,16 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1353,13 +1354,13 @@
         <v>35</v>
       </c>
       <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
         <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>24</v>
       </c>
       <c r="F21">
         <v>100000</v>
@@ -1368,16 +1369,16 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
       </c>
       <c r="K21" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1391,10 +1392,10 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F22">
         <v>75</v>
@@ -1406,13 +1407,13 @@
         <v>45</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
       </c>
       <c r="K22" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1423,13 +1424,13 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F23">
         <v>150</v>
@@ -1441,13 +1442,13 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
       </c>
       <c r="K23" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1458,13 +1459,13 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F24">
         <v>60</v>
@@ -1473,16 +1474,16 @@
         <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
       </c>
       <c r="K24" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1493,13 +1494,13 @@
         <v>44</v>
       </c>
       <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
         <v>28</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" t="s">
-        <v>24</v>
       </c>
       <c r="F25">
         <v>100000</v>
@@ -1508,16 +1509,16 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
       </c>
       <c r="K25" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1546,13 +1547,13 @@
         <v>47</v>
       </c>
       <c r="I26" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
       </c>
       <c r="K26" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1563,7 +1564,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -1581,13 +1582,13 @@
         <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
         <v>17</v>
       </c>
       <c r="K27" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1616,13 +1617,13 @@
         <v>49</v>
       </c>
       <c r="I28" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
       </c>
       <c r="K28" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1633,7 +1634,7 @@
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -1651,13 +1652,13 @@
         <v>50</v>
       </c>
       <c r="I29" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
       </c>
       <c r="K29" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1674,7 +1675,7 @@
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30">
         <v>25</v>
@@ -1686,13 +1687,13 @@
         <v>51</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
       </c>
       <c r="K30" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1703,13 +1704,13 @@
         <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31">
         <v>50</v>
@@ -1721,13 +1722,13 @@
         <v>52</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
       </c>
       <c r="K31" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1741,10 +1742,10 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F32">
         <v>75</v>
@@ -1756,13 +1757,13 @@
         <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
       </c>
       <c r="K32" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1773,13 +1774,13 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F33">
         <v>150</v>
@@ -1791,13 +1792,13 @@
         <v>55</v>
       </c>
       <c r="I33" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J33" t="s">
         <v>17</v>
       </c>
       <c r="K33" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1808,13 +1809,13 @@
         <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F34">
         <v>60</v>
@@ -1823,16 +1824,16 @@
         <v>3</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J34" t="s">
         <v>17</v>
       </c>
       <c r="K34" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1843,13 +1844,13 @@
         <v>53</v>
       </c>
       <c r="C35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" t="s">
         <v>28</v>
-      </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" t="s">
-        <v>24</v>
       </c>
       <c r="F35">
         <v>100000</v>
@@ -1858,16 +1859,16 @@
         <v>2153085</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J35" t="s">
         <v>17</v>
       </c>
       <c r="K35" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1896,13 +1897,13 @@
         <v>56</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
       </c>
       <c r="K36" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -1913,7 +1914,7 @@
         <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
@@ -1931,13 +1932,13 @@
         <v>57</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J37" t="s">
         <v>17</v>
       </c>
       <c r="K37" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1966,13 +1967,13 @@
         <v>58</v>
       </c>
       <c r="I38" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
       </c>
       <c r="K38" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -1983,7 +1984,7 @@
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -2001,13 +2002,13 @@
         <v>59</v>
       </c>
       <c r="I39" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
       </c>
       <c r="K39" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2024,7 +2025,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F40">
         <v>25</v>
@@ -2036,13 +2037,13 @@
         <v>60</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
       </c>
       <c r="K40" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2053,13 +2054,13 @@
         <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F41">
         <v>50</v>
@@ -2071,13 +2072,13 @@
         <v>61</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J41" t="s">
         <v>17</v>
       </c>
       <c r="K41" s="2">
-        <v>46195.587666611427</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2091,10 +2092,10 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F42">
         <v>75</v>
@@ -2106,7 +2107,7 @@
         <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
@@ -2123,13 +2124,13 @@
         <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F43">
         <v>150</v>
@@ -2138,10 +2139,10 @@
         <v>174</v>
       </c>
       <c r="H43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J43" t="s">
         <v>17</v>
@@ -2158,13 +2159,13 @@
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F44">
         <v>60</v>
@@ -2173,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" t="s">
         <v>17</v>
@@ -2193,13 +2194,13 @@
         <v>62</v>
       </c>
       <c r="C45" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" t="s">
         <v>28</v>
-      </c>
-      <c r="D45" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" t="s">
-        <v>24</v>
       </c>
       <c r="F45">
         <v>100000</v>
@@ -2208,10 +2209,10 @@
         <v>259090</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J45" t="s">
         <v>17</v>
@@ -2246,7 +2247,7 @@
         <v>64</v>
       </c>
       <c r="I46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J46" t="s">
         <v>17</v>
@@ -2263,7 +2264,7 @@
         <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -2278,10 +2279,10 @@
         <v>52</v>
       </c>
       <c r="H47" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
@@ -2316,7 +2317,7 @@
         <v>65</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
@@ -2333,7 +2334,7 @@
         <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2351,7 +2352,7 @@
         <v>59</v>
       </c>
       <c r="I49" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J49" t="s">
         <v>17</v>
@@ -2374,7 +2375,7 @@
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F50">
         <v>25</v>
@@ -2386,7 +2387,7 @@
         <v>66</v>
       </c>
       <c r="I50" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J50" t="s">
         <v>17</v>
@@ -2403,13 +2404,13 @@
         <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -2421,7 +2422,7 @@
         <v>67</v>
       </c>
       <c r="I51" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J51" t="s">
         <v>17</v>
@@ -2456,7 +2457,7 @@
         <v>66</v>
       </c>
       <c r="I52" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J52" t="s">
         <v>17</v>
@@ -2473,7 +2474,7 @@
         <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2488,10 +2489,10 @@
         <v>52</v>
       </c>
       <c r="H53" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I53" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J53" t="s">
         <v>17</v>
@@ -2511,10 +2512,10 @@
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F54">
         <v>75</v>
@@ -2526,7 +2527,7 @@
         <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J54" t="s">
         <v>17</v>
@@ -2543,13 +2544,13 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F55">
         <v>150</v>
@@ -2561,7 +2562,7 @@
         <v>69</v>
       </c>
       <c r="I55" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J55" t="s">
         <v>17</v>
@@ -2578,13 +2579,13 @@
         <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F56">
         <v>60</v>
@@ -2593,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s">
         <v>17</v>
@@ -2613,13 +2614,13 @@
         <v>68</v>
       </c>
       <c r="C57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" t="s">
         <v>28</v>
-      </c>
-      <c r="D57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" t="s">
-        <v>24</v>
       </c>
       <c r="F57">
         <v>100000</v>
@@ -2628,10 +2629,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
@@ -2666,7 +2667,7 @@
         <v>70</v>
       </c>
       <c r="I58" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
@@ -2683,7 +2684,7 @@
         <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -2701,7 +2702,7 @@
         <v>71</v>
       </c>
       <c r="I59" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J59" t="s">
         <v>17</v>
@@ -2736,7 +2737,7 @@
         <v>72</v>
       </c>
       <c r="I60" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
@@ -2753,7 +2754,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -2771,7 +2772,7 @@
         <v>65</v>
       </c>
       <c r="I61" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J61" t="s">
         <v>17</v>
@@ -2794,7 +2795,7 @@
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F62">
         <v>25</v>
@@ -2803,10 +2804,10 @@
         <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I62" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J62" t="s">
         <v>17</v>
@@ -2823,13 +2824,13 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F63">
         <v>50</v>
@@ -2841,7 +2842,7 @@
         <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J63" t="s">
         <v>17</v>
@@ -2861,10 +2862,10 @@
         <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F64">
         <v>45</v>
@@ -2876,13 +2877,13 @@
         <v>75</v>
       </c>
       <c r="I64" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J64" t="s">
         <v>17</v>
       </c>
       <c r="K64" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2893,13 +2894,13 @@
         <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F65">
         <v>150</v>
@@ -2911,13 +2912,13 @@
         <v>59</v>
       </c>
       <c r="I65" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J65" t="s">
         <v>17</v>
       </c>
       <c r="K65" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2928,13 +2929,13 @@
         <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F66">
         <v>60</v>
@@ -2943,16 +2944,16 @@
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
       </c>
       <c r="K66" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2963,13 +2964,13 @@
         <v>74</v>
       </c>
       <c r="C67" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" t="s">
         <v>28</v>
-      </c>
-      <c r="D67" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" t="s">
-        <v>24</v>
       </c>
       <c r="F67">
         <v>100000</v>
@@ -2978,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J67" t="s">
         <v>17</v>
       </c>
       <c r="K67" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -3016,13 +3017,13 @@
         <v>76</v>
       </c>
       <c r="I68" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J68" t="s">
         <v>17</v>
       </c>
       <c r="K68" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -3033,7 +3034,7 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3051,13 +3052,13 @@
         <v>77</v>
       </c>
       <c r="I69" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
       </c>
       <c r="K69" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -3074,7 +3075,7 @@
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F70">
         <v>25</v>
@@ -3086,13 +3087,13 @@
         <v>60</v>
       </c>
       <c r="I70" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
       </c>
       <c r="K70" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -3103,13 +3104,13 @@
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F71">
         <v>50</v>
@@ -3121,13 +3122,573 @@
         <v>78</v>
       </c>
       <c r="I71" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
       </c>
       <c r="K71" s="2">
-        <v>46255.761959169773</v>
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2026</v>
+      </c>
+      <c r="B72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72">
+        <v>75</v>
+      </c>
+      <c r="G72">
+        <v>42</v>
+      </c>
+      <c r="H72" t="s">
+        <v>51</v>
+      </c>
+      <c r="I72" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2026</v>
+      </c>
+      <c r="B73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73">
+        <v>150</v>
+      </c>
+      <c r="G73">
+        <v>141</v>
+      </c>
+      <c r="H73" t="s">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2026</v>
+      </c>
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74">
+        <v>60</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2026</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75">
+        <v>100000</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2026</v>
+      </c>
+      <c r="B76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76">
+        <v>25</v>
+      </c>
+      <c r="G76">
+        <v>23</v>
+      </c>
+      <c r="H76" t="s">
+        <v>81</v>
+      </c>
+      <c r="I76" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2026</v>
+      </c>
+      <c r="B77" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77">
+        <v>50</v>
+      </c>
+      <c r="G77">
+        <v>69</v>
+      </c>
+      <c r="H77" t="s">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2026</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78">
+        <v>25</v>
+      </c>
+      <c r="G78">
+        <v>16</v>
+      </c>
+      <c r="H78" t="s">
+        <v>56</v>
+      </c>
+      <c r="I78" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2026</v>
+      </c>
+      <c r="B79" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79">
+        <v>50</v>
+      </c>
+      <c r="G79">
+        <v>68</v>
+      </c>
+      <c r="H79" t="s">
+        <v>83</v>
+      </c>
+      <c r="I79" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" s="2">
+        <v>46286.795092314816</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2026</v>
+      </c>
+      <c r="B80" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80">
+        <v>75</v>
+      </c>
+      <c r="G80">
+        <v>42</v>
+      </c>
+      <c r="H80" t="s">
+        <v>51</v>
+      </c>
+      <c r="I80" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80" s="2">
+        <v>46286.795256544377</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2026</v>
+      </c>
+      <c r="B81" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81">
+        <v>150</v>
+      </c>
+      <c r="G81">
+        <v>141</v>
+      </c>
+      <c r="H81" t="s">
+        <v>80</v>
+      </c>
+      <c r="I81" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="2">
+        <v>46286.795256544377</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82">
+        <v>60</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82" s="2">
+        <v>46286.795256544377</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2026</v>
+      </c>
+      <c r="B83" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83">
+        <v>100000</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="2">
+        <v>46286.795256544377</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2026</v>
+      </c>
+      <c r="B84" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84">
+        <v>25</v>
+      </c>
+      <c r="G84">
+        <v>23</v>
+      </c>
+      <c r="H84" t="s">
+        <v>81</v>
+      </c>
+      <c r="I84" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" s="2">
+        <v>46286.795256544377</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2026</v>
+      </c>
+      <c r="B85" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85">
+        <v>50</v>
+      </c>
+      <c r="G85">
+        <v>69</v>
+      </c>
+      <c r="H85" t="s">
+        <v>82</v>
+      </c>
+      <c r="I85" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85" s="2">
+        <v>46286.795256544377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2026</v>
+      </c>
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>21</v>
+      </c>
+      <c r="F86">
+        <v>25</v>
+      </c>
+      <c r="G86">
+        <v>16</v>
+      </c>
+      <c r="H86" t="s">
+        <v>56</v>
+      </c>
+      <c r="I86" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" s="2">
+        <v>46286.795256544377</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2026</v>
+      </c>
+      <c r="B87" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87">
+        <v>50</v>
+      </c>
+      <c r="G87">
+        <v>68</v>
+      </c>
+      <c r="H87" t="s">
+        <v>83</v>
+      </c>
+      <c r="I87" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="2">
+        <v>46286.795256544377</v>
       </c>
     </row>
   </sheetData>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/08 Agosto/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE224B8-4484-4D30-92DF-D2631A2CE667}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E69C2C3-9ADB-42E2-B2D3-5C8DF70A31B5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="87">
   <si>
     <t>Año</t>
   </si>
@@ -272,6 +272,15 @@
   </si>
   <si>
     <t>136.0%</t>
+  </si>
+  <si>
+    <t>93.3%</t>
+  </si>
+  <si>
+    <t>106.7%</t>
+  </si>
+  <si>
+    <t>97.1%</t>
   </si>
 </sst>
 </file>
@@ -279,9 +288,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,6 +303,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -331,12 +345,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -639,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -682,38 +699,38 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2026</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2">
-        <v>20</v>
-      </c>
-      <c r="G2">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2">
-        <v>46070.812099907409</v>
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -730,19 +747,19 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -765,16 +782,16 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>20</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -794,25 +811,25 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -835,16 +852,16 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>40</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -870,19 +887,19 @@
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F7">
         <v>40</v>
       </c>
       <c r="G7">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -899,22 +916,22 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G8">
-        <v>26.5</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
@@ -934,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -943,16 +960,16 @@
         <v>28</v>
       </c>
       <c r="F9">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>185</v>
+        <v>26.5</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -969,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
@@ -978,16 +995,16 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G10">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -1004,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
@@ -1016,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -1036,34 +1053,34 @@
         <v>2026</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="2">
-        <v>46099.788829444442</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1074,7 +1091,7 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1083,13 +1100,13 @@
         <v>14</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G13">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>
@@ -1109,25 +1126,25 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1144,7 +1161,7 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1153,13 +1170,13 @@
         <v>18</v>
       </c>
       <c r="F15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G15">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
@@ -1179,22 +1196,22 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G16">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
@@ -1214,7 +1231,7 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -1223,13 +1240,13 @@
         <v>21</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G17">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I17" t="s">
         <v>20</v>
@@ -1249,22 +1266,22 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F18">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G18">
-        <v>60.5</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I18" t="s">
         <v>20</v>
@@ -1284,7 +1301,7 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -1293,16 +1310,16 @@
         <v>28</v>
       </c>
       <c r="F19">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>170</v>
+        <v>60.5</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -1319,7 +1336,7 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -1328,16 +1345,16 @@
         <v>28</v>
       </c>
       <c r="F20">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -1354,7 +1371,7 @@
         <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -1363,10 +1380,10 @@
         <v>28</v>
       </c>
       <c r="F21">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="s">
         <v>20</v>
@@ -1386,10 +1403,10 @@
         <v>2026</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -1398,13 +1415,13 @@
         <v>28</v>
       </c>
       <c r="F22">
-        <v>75</v>
+        <v>100000</v>
       </c>
       <c r="G22">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -1413,7 +1430,7 @@
         <v>17</v>
       </c>
       <c r="K22" s="2">
-        <v>46135.554853842586</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1424,7 +1441,7 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -1433,16 +1450,16 @@
         <v>28</v>
       </c>
       <c r="F23">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G23">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -1459,7 +1476,7 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -1468,13 +1485,13 @@
         <v>28</v>
       </c>
       <c r="F24">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G24">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I24" t="s">
         <v>16</v>
@@ -1494,7 +1511,7 @@
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -1503,16 +1520,16 @@
         <v>28</v>
       </c>
       <c r="F25">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H25" t="s">
         <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
@@ -1529,25 +1546,25 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>100000</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
@@ -1564,7 +1581,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -1573,13 +1590,13 @@
         <v>14</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G27">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
@@ -1599,22 +1616,22 @@
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I28" t="s">
         <v>16</v>
@@ -1634,7 +1651,7 @@
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -1643,13 +1660,13 @@
         <v>18</v>
       </c>
       <c r="F29">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G29">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I29" t="s">
         <v>16</v>
@@ -1669,25 +1686,25 @@
         <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F30">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G30">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="H30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
@@ -1704,7 +1721,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
@@ -1713,13 +1730,13 @@
         <v>21</v>
       </c>
       <c r="F31">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G31">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I31" t="s">
         <v>20</v>
@@ -1736,25 +1753,25 @@
         <v>2026</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G32">
-        <v>52.5</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I32" t="s">
         <v>20</v>
@@ -1763,7 +1780,7 @@
         <v>17</v>
       </c>
       <c r="K32" s="2">
-        <v>46195.587666608793</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1774,7 +1791,7 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -1783,16 +1800,16 @@
         <v>28</v>
       </c>
       <c r="F33">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G33">
-        <v>163</v>
+        <v>52.5</v>
       </c>
       <c r="H33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J33" t="s">
         <v>17</v>
@@ -1809,7 +1826,7 @@
         <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -1818,13 +1835,13 @@
         <v>28</v>
       </c>
       <c r="F34">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I34" t="s">
         <v>16</v>
@@ -1844,7 +1861,7 @@
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -1853,10 +1870,10 @@
         <v>28</v>
       </c>
       <c r="F35">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G35">
-        <v>2153085</v>
+        <v>3</v>
       </c>
       <c r="H35" t="s">
         <v>20</v>
@@ -1879,25 +1896,25 @@
         <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="G36">
-        <v>16</v>
+        <v>2153085</v>
       </c>
       <c r="H36" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
@@ -1914,7 +1931,7 @@
         <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
@@ -1923,13 +1940,13 @@
         <v>14</v>
       </c>
       <c r="F37">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G37">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I37" t="s">
         <v>20</v>
@@ -1949,25 +1966,25 @@
         <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G38">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I38" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
@@ -1984,7 +2001,7 @@
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -1993,16 +2010,16 @@
         <v>18</v>
       </c>
       <c r="F39">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G39">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="H39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
@@ -2019,25 +2036,25 @@
         <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F40">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="H40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
@@ -2054,7 +2071,7 @@
         <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
@@ -2063,13 +2080,13 @@
         <v>21</v>
       </c>
       <c r="F41">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G41">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I41" t="s">
         <v>20</v>
@@ -2086,34 +2103,34 @@
         <v>2026</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F42">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G42">
-        <v>75.5</v>
+        <v>50</v>
       </c>
       <c r="H42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
       </c>
       <c r="K42" s="2">
-        <v>46195.596720196758</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2124,7 +2141,7 @@
         <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -2133,13 +2150,13 @@
         <v>28</v>
       </c>
       <c r="F43">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G43">
-        <v>174</v>
+        <v>75.5</v>
       </c>
       <c r="H43" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
         <v>16</v>
@@ -2159,7 +2176,7 @@
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -2168,16 +2185,16 @@
         <v>28</v>
       </c>
       <c r="F44">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J44" t="s">
         <v>17</v>
@@ -2194,7 +2211,7 @@
         <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -2203,10 +2220,10 @@
         <v>28</v>
       </c>
       <c r="F45">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G45">
-        <v>259090</v>
+        <v>0</v>
       </c>
       <c r="H45" t="s">
         <v>20</v>
@@ -2229,22 +2246,22 @@
         <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F46">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="G46">
-        <v>18</v>
+        <v>259090</v>
       </c>
       <c r="H46" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
@@ -2264,7 +2281,7 @@
         <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -2273,13 +2290,13 @@
         <v>14</v>
       </c>
       <c r="F47">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G47">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="H47" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
@@ -2299,22 +2316,22 @@
         <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F48">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G48">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="H48" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
@@ -2334,7 +2351,7 @@
         <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2343,16 +2360,16 @@
         <v>18</v>
       </c>
       <c r="F49">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G49">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="H49" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" t="s">
         <v>17</v>
@@ -2369,22 +2386,22 @@
         <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F50">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G50">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="H50" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I50" t="s">
         <v>16</v>
@@ -2404,7 +2421,7 @@
         <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -2413,13 +2430,13 @@
         <v>21</v>
       </c>
       <c r="F51">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G51">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I51" t="s">
         <v>16</v>
@@ -2439,22 +2456,22 @@
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F52">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G52">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="H52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I52" t="s">
         <v>16</v>
@@ -2463,7 +2480,7 @@
         <v>17</v>
       </c>
       <c r="K52" s="2">
-        <v>46226.635234062502</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2474,7 +2491,7 @@
         <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2483,13 +2500,13 @@
         <v>14</v>
       </c>
       <c r="F53">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G53">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="I53" t="s">
         <v>16</v>
@@ -2506,25 +2523,25 @@
         <v>2026</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F54">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G54">
-        <v>75.5</v>
+        <v>52</v>
       </c>
       <c r="H54" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="I54" t="s">
         <v>16</v>
@@ -2533,7 +2550,7 @@
         <v>17</v>
       </c>
       <c r="K54" s="2">
-        <v>46226.635931354169</v>
+        <v>46226.635234062502</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2544,7 +2561,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -2553,13 +2570,13 @@
         <v>28</v>
       </c>
       <c r="F55">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G55">
-        <v>159</v>
+        <v>75.5</v>
       </c>
       <c r="H55" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
         <v>16</v>
@@ -2579,7 +2596,7 @@
         <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -2588,16 +2605,16 @@
         <v>28</v>
       </c>
       <c r="F56">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H56" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J56" t="s">
         <v>17</v>
@@ -2614,7 +2631,7 @@
         <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -2623,7 +2640,7 @@
         <v>28</v>
       </c>
       <c r="F57">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2649,25 +2666,25 @@
         <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E58" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F58">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="G58">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="I58" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
@@ -2684,7 +2701,7 @@
         <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -2693,13 +2710,13 @@
         <v>14</v>
       </c>
       <c r="F59">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G59">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="H59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I59" t="s">
         <v>16</v>
@@ -2719,25 +2736,25 @@
         <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F60">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G60">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
@@ -2754,7 +2771,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -2763,13 +2780,13 @@
         <v>18</v>
       </c>
       <c r="F61">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G61">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H61" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
@@ -2789,22 +2806,22 @@
         <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F62">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G62">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H62" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
@@ -2824,7 +2841,7 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -2833,13 +2850,13 @@
         <v>21</v>
       </c>
       <c r="F63">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G63">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="I63" t="s">
         <v>20</v>
@@ -2856,34 +2873,34 @@
         <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F64">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G64">
-        <v>41.5</v>
+        <v>39</v>
       </c>
       <c r="H64" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J64" t="s">
         <v>17</v>
       </c>
       <c r="K64" s="2">
-        <v>46255.761959166673</v>
+        <v>46226.635931354169</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2894,7 +2911,7 @@
         <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D65" t="s">
         <v>27</v>
@@ -2903,13 +2920,13 @@
         <v>28</v>
       </c>
       <c r="F65">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="G65">
-        <v>171</v>
+        <v>41.5</v>
       </c>
       <c r="H65" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I65" t="s">
         <v>16</v>
@@ -2929,7 +2946,7 @@
         <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
         <v>27</v>
@@ -2938,16 +2955,16 @@
         <v>28</v>
       </c>
       <c r="F66">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="I66" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
@@ -2964,7 +2981,7 @@
         <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D67" t="s">
         <v>27</v>
@@ -2973,7 +2990,7 @@
         <v>28</v>
       </c>
       <c r="F67">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2999,25 +3016,25 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E68" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F68">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="G68">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I68" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J68" t="s">
         <v>17</v>
@@ -3034,7 +3051,7 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3043,13 +3060,13 @@
         <v>14</v>
       </c>
       <c r="F69">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G69">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="H69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I69" t="s">
         <v>16</v>
@@ -3069,25 +3086,25 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F70">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G70">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="H70" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
@@ -3104,7 +3121,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3113,16 +3130,16 @@
         <v>21</v>
       </c>
       <c r="F71">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G71">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="H71" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="I71" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
@@ -3136,25 +3153,25 @@
         <v>2026</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C72" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F72">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G72">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H72" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="I72" t="s">
         <v>16</v>
@@ -3163,7 +3180,7 @@
         <v>17</v>
       </c>
       <c r="K72" s="2">
-        <v>46286.795092314816</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3174,7 +3191,7 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
         <v>27</v>
@@ -3183,13 +3200,13 @@
         <v>28</v>
       </c>
       <c r="F73">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G73">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="H73" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="I73" t="s">
         <v>16</v>
@@ -3209,7 +3226,7 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
         <v>27</v>
@@ -3218,16 +3235,16 @@
         <v>28</v>
       </c>
       <c r="F74">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
@@ -3244,7 +3261,7 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D75" t="s">
         <v>27</v>
@@ -3253,7 +3270,7 @@
         <v>28</v>
       </c>
       <c r="F75">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3279,25 +3296,25 @@
         <v>79</v>
       </c>
       <c r="C76" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E76" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F76">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="G76">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J76" t="s">
         <v>17</v>
@@ -3314,7 +3331,7 @@
         <v>79</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -3323,13 +3340,13 @@
         <v>14</v>
       </c>
       <c r="F77">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G77">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="H77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I77" t="s">
         <v>16</v>
@@ -3349,22 +3366,22 @@
         <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F78">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G78">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="H78" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="I78" t="s">
         <v>16</v>
@@ -3384,7 +3401,7 @@
         <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -3393,13 +3410,13 @@
         <v>21</v>
       </c>
       <c r="F79">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G79">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="H79" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="I79" t="s">
         <v>16</v>
@@ -3419,22 +3436,22 @@
         <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F80">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G80">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="H80" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="I80" t="s">
         <v>16</v>
@@ -3443,7 +3460,7 @@
         <v>17</v>
       </c>
       <c r="K80" s="2">
-        <v>46286.795256544377</v>
+        <v>46286.795092314816</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -3454,7 +3471,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
         <v>27</v>
@@ -3463,13 +3480,13 @@
         <v>28</v>
       </c>
       <c r="F81">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G81">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="H81" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="I81" t="s">
         <v>16</v>
@@ -3478,7 +3495,7 @@
         <v>17</v>
       </c>
       <c r="K81" s="2">
-        <v>46286.795256544377</v>
+        <v>46286.79525653935</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -3489,7 +3506,7 @@
         <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>27</v>
@@ -3498,22 +3515,22 @@
         <v>28</v>
       </c>
       <c r="F82">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I82" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
       </c>
       <c r="K82" s="2">
-        <v>46286.795256544377</v>
+        <v>46286.79525653935</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -3524,7 +3541,7 @@
         <v>79</v>
       </c>
       <c r="C83" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D83" t="s">
         <v>27</v>
@@ -3533,7 +3550,7 @@
         <v>28</v>
       </c>
       <c r="F83">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -3548,7 +3565,7 @@
         <v>17</v>
       </c>
       <c r="K83" s="2">
-        <v>46286.795256544377</v>
+        <v>46286.79525653935</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -3559,31 +3576,31 @@
         <v>79</v>
       </c>
       <c r="C84" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F84">
-        <v>25</v>
+        <v>100000</v>
       </c>
       <c r="G84">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
       </c>
       <c r="K84" s="2">
-        <v>46286.795256544377</v>
+        <v>46286.79525653935</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -3594,7 +3611,7 @@
         <v>79</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -3603,13 +3620,13 @@
         <v>14</v>
       </c>
       <c r="F85">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G85">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="H85" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I85" t="s">
         <v>16</v>
@@ -3618,7 +3635,7 @@
         <v>17</v>
       </c>
       <c r="K85" s="2">
-        <v>46286.795256544377</v>
+        <v>46286.79525653935</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -3629,22 +3646,22 @@
         <v>79</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F86">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G86">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="H86" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="I86" t="s">
         <v>16</v>
@@ -3653,7 +3670,7 @@
         <v>17</v>
       </c>
       <c r="K86" s="2">
-        <v>46286.795256544377</v>
+        <v>46286.79525653935</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -3664,7 +3681,7 @@
         <v>79</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
         <v>13</v>
@@ -3673,22 +3690,337 @@
         <v>21</v>
       </c>
       <c r="F87">
+        <v>25</v>
+      </c>
+      <c r="G87">
+        <v>16</v>
+      </c>
+      <c r="H87" t="s">
+        <v>56</v>
+      </c>
+      <c r="I87" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="2">
+        <v>46286.79525653935</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2026</v>
+      </c>
+      <c r="B88" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88">
         <v>50</v>
       </c>
-      <c r="G87">
+      <c r="G88">
         <v>68</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H88" t="s">
         <v>83</v>
       </c>
-      <c r="I87" t="s">
-        <v>16</v>
-      </c>
-      <c r="J87" t="s">
-        <v>17</v>
-      </c>
-      <c r="K87" s="2">
-        <v>46286.795256544377</v>
+      <c r="I88" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" t="s">
+        <v>17</v>
+      </c>
+      <c r="K88" s="2">
+        <v>46286.79525653935</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2026</v>
+      </c>
+      <c r="B89" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" t="s">
+        <v>28</v>
+      </c>
+      <c r="F89">
+        <v>45</v>
+      </c>
+      <c r="G89">
+        <v>42</v>
+      </c>
+      <c r="H89" t="s">
+        <v>84</v>
+      </c>
+      <c r="I89" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>2026</v>
+      </c>
+      <c r="B90" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" t="s">
+        <v>28</v>
+      </c>
+      <c r="F90">
+        <v>150</v>
+      </c>
+      <c r="G90">
+        <v>141</v>
+      </c>
+      <c r="H90" t="s">
+        <v>80</v>
+      </c>
+      <c r="I90" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2026</v>
+      </c>
+      <c r="B91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" t="s">
+        <v>32</v>
+      </c>
+      <c r="D91" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" t="s">
+        <v>28</v>
+      </c>
+      <c r="F91">
+        <v>60</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>2026</v>
+      </c>
+      <c r="B92" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="s">
+        <v>27</v>
+      </c>
+      <c r="E92" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92">
+        <v>100000</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" t="s">
+        <v>17</v>
+      </c>
+      <c r="K92" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>2026</v>
+      </c>
+      <c r="B93" t="s">
+        <v>79</v>
+      </c>
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93">
+        <v>25</v>
+      </c>
+      <c r="G93">
+        <v>23</v>
+      </c>
+      <c r="H93" t="s">
+        <v>81</v>
+      </c>
+      <c r="I93" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" t="s">
+        <v>17</v>
+      </c>
+      <c r="K93" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>2026</v>
+      </c>
+      <c r="B94" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94">
+        <v>50</v>
+      </c>
+      <c r="G94">
+        <v>69</v>
+      </c>
+      <c r="H94" t="s">
+        <v>82</v>
+      </c>
+      <c r="I94" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>2026</v>
+      </c>
+      <c r="B95" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95">
+        <v>15</v>
+      </c>
+      <c r="G95">
+        <v>16</v>
+      </c>
+      <c r="H95" t="s">
+        <v>85</v>
+      </c>
+      <c r="I95" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" t="s">
+        <v>17</v>
+      </c>
+      <c r="K95" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>2026</v>
+      </c>
+      <c r="B96" t="s">
+        <v>79</v>
+      </c>
+      <c r="C96" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96">
+        <v>70</v>
+      </c>
+      <c r="G96">
+        <v>68</v>
+      </c>
+      <c r="H96" t="s">
+        <v>86</v>
+      </c>
+      <c r="I96" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" t="s">
+        <v>17</v>
+      </c>
+      <c r="K96" s="2">
+        <v>46287.5689004245</v>
       </c>
     </row>
   </sheetData>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/08 Agosto/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E69C2C3-9ADB-42E2-B2D3-5C8DF70A31B5}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02448D08-70F2-464B-8717-BC1FFDD0993E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="87">
   <si>
     <t>Año</t>
   </si>
@@ -290,7 +290,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,11 +303,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -345,15 +340,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -699,38 +691,38 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>10</v>
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -747,19 +739,19 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -782,16 +774,16 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>20</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -811,25 +803,25 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -852,16 +844,16 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6">
         <v>40</v>
       </c>
       <c r="G6">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -887,19 +879,19 @@
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>40</v>
       </c>
       <c r="G7">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -916,22 +908,22 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>26.5</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
@@ -951,7 +943,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -960,16 +952,16 @@
         <v>28</v>
       </c>
       <c r="F9">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="G9">
-        <v>26.5</v>
+        <v>185</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -986,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
@@ -995,16 +987,16 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -1021,7 +1013,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
@@ -1033,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -1053,34 +1045,34 @@
         <v>2026</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="2">
-        <v>46070.812099907409</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1091,7 +1083,7 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -1100,13 +1092,13 @@
         <v>14</v>
       </c>
       <c r="F13">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G13">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>
@@ -1126,25 +1118,25 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G14">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1161,7 +1153,7 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1170,13 +1162,13 @@
         <v>18</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G15">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
@@ -1196,22 +1188,22 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G16">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
@@ -1231,7 +1223,7 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -1240,13 +1232,13 @@
         <v>21</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
         <v>20</v>
@@ -1266,22 +1258,22 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G18">
-        <v>52</v>
+        <v>60.5</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I18" t="s">
         <v>20</v>
@@ -1301,7 +1293,7 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -1310,16 +1302,16 @@
         <v>28</v>
       </c>
       <c r="F19">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G19">
-        <v>60.5</v>
+        <v>170</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -1336,7 +1328,7 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -1345,16 +1337,16 @@
         <v>28</v>
       </c>
       <c r="F20">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G20">
-        <v>170</v>
+        <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
@@ -1371,7 +1363,7 @@
         <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -1380,10 +1372,10 @@
         <v>28</v>
       </c>
       <c r="F21">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="s">
         <v>20</v>
@@ -1403,10 +1395,10 @@
         <v>2026</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -1415,13 +1407,13 @@
         <v>28</v>
       </c>
       <c r="F22">
-        <v>100000</v>
+        <v>75</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -1430,7 +1422,7 @@
         <v>17</v>
       </c>
       <c r="K22" s="2">
-        <v>46099.788829444442</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1441,7 +1433,7 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -1450,16 +1442,16 @@
         <v>28</v>
       </c>
       <c r="F23">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G23">
+        <v>169</v>
+      </c>
+      <c r="H23" t="s">
         <v>46</v>
       </c>
-      <c r="H23" t="s">
-        <v>45</v>
-      </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -1476,7 +1468,7 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -1485,13 +1477,13 @@
         <v>28</v>
       </c>
       <c r="F24">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G24">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I24" t="s">
         <v>16</v>
@@ -1511,7 +1503,7 @@
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -1520,16 +1512,16 @@
         <v>28</v>
       </c>
       <c r="F25">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G25">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H25" t="s">
         <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
@@ -1546,25 +1538,25 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F26">
-        <v>100000</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
@@ -1581,7 +1573,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -1590,13 +1582,13 @@
         <v>14</v>
       </c>
       <c r="F27">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G27">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s">
         <v>16</v>
@@ -1616,22 +1608,22 @@
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G28">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I28" t="s">
         <v>16</v>
@@ -1651,7 +1643,7 @@
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -1660,13 +1652,13 @@
         <v>18</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G29">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I29" t="s">
         <v>16</v>
@@ -1686,25 +1678,25 @@
         <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G30">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
@@ -1721,7 +1713,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
@@ -1730,13 +1722,13 @@
         <v>21</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G31">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I31" t="s">
         <v>20</v>
@@ -1753,25 +1745,25 @@
         <v>2026</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G32">
-        <v>79</v>
+        <v>52.5</v>
       </c>
       <c r="H32" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
         <v>20</v>
@@ -1780,7 +1772,7 @@
         <v>17</v>
       </c>
       <c r="K32" s="2">
-        <v>46135.554853842586</v>
+        <v>46195.587666608793</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1791,7 +1783,7 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -1800,16 +1792,16 @@
         <v>28</v>
       </c>
       <c r="F33">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G33">
-        <v>52.5</v>
+        <v>163</v>
       </c>
       <c r="H33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I33" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" t="s">
         <v>17</v>
@@ -1826,7 +1818,7 @@
         <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -1835,13 +1827,13 @@
         <v>28</v>
       </c>
       <c r="F34">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G34">
-        <v>163</v>
+        <v>3</v>
       </c>
       <c r="H34" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="I34" t="s">
         <v>16</v>
@@ -1861,7 +1853,7 @@
         <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -1870,10 +1862,10 @@
         <v>28</v>
       </c>
       <c r="F35">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2153085</v>
       </c>
       <c r="H35" t="s">
         <v>20</v>
@@ -1896,25 +1888,25 @@
         <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F36">
-        <v>100000</v>
+        <v>25</v>
       </c>
       <c r="G36">
-        <v>2153085</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
@@ -1931,7 +1923,7 @@
         <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
@@ -1940,13 +1932,13 @@
         <v>14</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G37">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="H37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I37" t="s">
         <v>20</v>
@@ -1966,25 +1958,25 @@
         <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F38">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G38">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
@@ -2001,7 +1993,7 @@
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -2010,16 +2002,16 @@
         <v>18</v>
       </c>
       <c r="F39">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G39">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I39" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
@@ -2036,25 +2028,25 @@
         <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F40">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G40">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="H40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
@@ -2071,7 +2063,7 @@
         <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
@@ -2080,13 +2072,13 @@
         <v>21</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I41" t="s">
         <v>20</v>
@@ -2103,34 +2095,34 @@
         <v>2026</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F42">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G42">
-        <v>50</v>
+        <v>75.5</v>
       </c>
       <c r="H42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
       </c>
       <c r="K42" s="2">
-        <v>46195.587666608793</v>
+        <v>46195.596720196758</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2141,7 +2133,7 @@
         <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -2150,13 +2142,13 @@
         <v>28</v>
       </c>
       <c r="F43">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G43">
-        <v>75.5</v>
+        <v>174</v>
       </c>
       <c r="H43" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I43" t="s">
         <v>16</v>
@@ -2176,7 +2168,7 @@
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -2185,16 +2177,16 @@
         <v>28</v>
       </c>
       <c r="F44">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G44">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" t="s">
         <v>17</v>
@@ -2211,7 +2203,7 @@
         <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -2220,10 +2212,10 @@
         <v>28</v>
       </c>
       <c r="F45">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>259090</v>
       </c>
       <c r="H45" t="s">
         <v>20</v>
@@ -2246,22 +2238,22 @@
         <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F46">
-        <v>100000</v>
+        <v>25</v>
       </c>
       <c r="G46">
-        <v>259090</v>
+        <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
@@ -2281,7 +2273,7 @@
         <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -2290,13 +2282,13 @@
         <v>14</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G47">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="H47" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
@@ -2316,22 +2308,22 @@
         <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F48">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G48">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="H48" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
@@ -2351,7 +2343,7 @@
         <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2360,16 +2352,16 @@
         <v>18</v>
       </c>
       <c r="F49">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G49">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="H49" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I49" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" t="s">
         <v>17</v>
@@ -2386,22 +2378,22 @@
         <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F50">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G50">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I50" t="s">
         <v>16</v>
@@ -2421,7 +2413,7 @@
         <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -2430,13 +2422,13 @@
         <v>21</v>
       </c>
       <c r="F51">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G51">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="H51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I51" t="s">
         <v>16</v>
@@ -2456,22 +2448,22 @@
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F52">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G52">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I52" t="s">
         <v>16</v>
@@ -2480,7 +2472,7 @@
         <v>17</v>
       </c>
       <c r="K52" s="2">
-        <v>46195.596720196758</v>
+        <v>46226.635234062502</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2491,7 +2483,7 @@
         <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2500,13 +2492,13 @@
         <v>14</v>
       </c>
       <c r="F53">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G53">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="H53" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="I53" t="s">
         <v>16</v>
@@ -2523,25 +2515,25 @@
         <v>2026</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E54" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F54">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G54">
-        <v>52</v>
+        <v>75.5</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
         <v>16</v>
@@ -2550,7 +2542,7 @@
         <v>17</v>
       </c>
       <c r="K54" s="2">
-        <v>46226.635234062502</v>
+        <v>46226.635931354169</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2561,7 +2553,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -2570,13 +2562,13 @@
         <v>28</v>
       </c>
       <c r="F55">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G55">
-        <v>75.5</v>
+        <v>159</v>
       </c>
       <c r="H55" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I55" t="s">
         <v>16</v>
@@ -2596,7 +2588,7 @@
         <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -2605,16 +2597,16 @@
         <v>28</v>
       </c>
       <c r="F56">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G56">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s">
         <v>17</v>
@@ -2631,7 +2623,7 @@
         <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -2640,7 +2632,7 @@
         <v>28</v>
       </c>
       <c r="F57">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2666,25 +2658,25 @@
         <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F58">
-        <v>100000</v>
+        <v>25</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H58" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
@@ -2701,7 +2693,7 @@
         <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -2710,13 +2702,13 @@
         <v>14</v>
       </c>
       <c r="F59">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G59">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I59" t="s">
         <v>16</v>
@@ -2736,25 +2728,25 @@
         <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F60">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G60">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="H60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I60" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
@@ -2771,7 +2763,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -2780,13 +2772,13 @@
         <v>18</v>
       </c>
       <c r="F61">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G61">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
@@ -2806,22 +2798,22 @@
         <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F62">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G62">
+        <v>17</v>
+      </c>
+      <c r="H62" t="s">
         <v>38</v>
-      </c>
-      <c r="H62" t="s">
-        <v>65</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
@@ -2841,7 +2833,7 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -2850,13 +2842,13 @@
         <v>21</v>
       </c>
       <c r="F63">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G63">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H63" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
         <v>20</v>
@@ -2873,34 +2865,34 @@
         <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F64">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G64">
-        <v>39</v>
+        <v>41.5</v>
       </c>
       <c r="H64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J64" t="s">
         <v>17</v>
       </c>
       <c r="K64" s="2">
-        <v>46226.635931354169</v>
+        <v>46255.761959166673</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2911,7 +2903,7 @@
         <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>27</v>
@@ -2920,13 +2912,13 @@
         <v>28</v>
       </c>
       <c r="F65">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="G65">
-        <v>41.5</v>
+        <v>171</v>
       </c>
       <c r="H65" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="I65" t="s">
         <v>16</v>
@@ -2946,7 +2938,7 @@
         <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
         <v>27</v>
@@ -2955,16 +2947,16 @@
         <v>28</v>
       </c>
       <c r="F66">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G66">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
@@ -2981,7 +2973,7 @@
         <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s">
         <v>27</v>
@@ -2990,7 +2982,7 @@
         <v>28</v>
       </c>
       <c r="F67">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3016,25 +3008,25 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F68">
-        <v>100000</v>
+        <v>25</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I68" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J68" t="s">
         <v>17</v>
@@ -3051,7 +3043,7 @@
         <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3060,13 +3052,13 @@
         <v>14</v>
       </c>
       <c r="F69">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G69">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="H69" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I69" t="s">
         <v>16</v>
@@ -3086,25 +3078,25 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F70">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G70">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="H70" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I70" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
@@ -3121,7 +3113,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3130,16 +3122,16 @@
         <v>21</v>
       </c>
       <c r="F71">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G71">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="H71" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I71" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
@@ -3153,25 +3145,25 @@
         <v>2026</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F72">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G72">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="H72" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="I72" t="s">
         <v>16</v>
@@ -3180,7 +3172,7 @@
         <v>17</v>
       </c>
       <c r="K72" s="2">
-        <v>46255.761959166673</v>
+        <v>46286.795092314816</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3191,7 +3183,7 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
         <v>27</v>
@@ -3200,13 +3192,13 @@
         <v>28</v>
       </c>
       <c r="F73">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G73">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H73" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I73" t="s">
         <v>16</v>
@@ -3226,7 +3218,7 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D74" t="s">
         <v>27</v>
@@ -3235,16 +3227,16 @@
         <v>28</v>
       </c>
       <c r="F74">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G74">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
@@ -3261,7 +3253,7 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D75" t="s">
         <v>27</v>
@@ -3270,7 +3262,7 @@
         <v>28</v>
       </c>
       <c r="F75">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3296,25 +3288,25 @@
         <v>79</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F76">
-        <v>100000</v>
+        <v>25</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J76" t="s">
         <v>17</v>
@@ -3331,7 +3323,7 @@
         <v>79</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -3340,13 +3332,13 @@
         <v>14</v>
       </c>
       <c r="F77">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G77">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I77" t="s">
         <v>16</v>
@@ -3366,22 +3358,22 @@
         <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F78">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G78">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="H78" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="I78" t="s">
         <v>16</v>
@@ -3401,7 +3393,7 @@
         <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D79" t="s">
         <v>13</v>
@@ -3410,13 +3402,13 @@
         <v>21</v>
       </c>
       <c r="F79">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G79">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="H79" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="I79" t="s">
         <v>16</v>
@@ -3436,22 +3428,22 @@
         <v>79</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F80">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G80">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="H80" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="I80" t="s">
         <v>16</v>
@@ -3460,7 +3452,7 @@
         <v>17</v>
       </c>
       <c r="K80" s="2">
-        <v>46286.795092314816</v>
+        <v>46286.79525653935</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -3471,7 +3463,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D81" t="s">
         <v>27</v>
@@ -3480,13 +3472,13 @@
         <v>28</v>
       </c>
       <c r="F81">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G81">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H81" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I81" t="s">
         <v>16</v>
@@ -3506,7 +3498,7 @@
         <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D82" t="s">
         <v>27</v>
@@ -3515,16 +3507,16 @@
         <v>28</v>
       </c>
       <c r="F82">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G82">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
@@ -3541,7 +3533,7 @@
         <v>79</v>
       </c>
       <c r="C83" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
         <v>27</v>
@@ -3550,7 +3542,7 @@
         <v>28</v>
       </c>
       <c r="F83">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -3576,25 +3568,25 @@
         <v>79</v>
       </c>
       <c r="C84" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F84">
-        <v>100000</v>
+        <v>25</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I84" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
@@ -3611,7 +3603,7 @@
         <v>79</v>
       </c>
       <c r="C85" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -3620,13 +3612,13 @@
         <v>14</v>
       </c>
       <c r="F85">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G85">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H85" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I85" t="s">
         <v>16</v>
@@ -3646,22 +3638,22 @@
         <v>79</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F86">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G86">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="H86" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="I86" t="s">
         <v>16</v>
@@ -3681,7 +3673,7 @@
         <v>79</v>
       </c>
       <c r="C87" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D87" t="s">
         <v>13</v>
@@ -3690,13 +3682,13 @@
         <v>21</v>
       </c>
       <c r="F87">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G87">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="H87" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="I87" t="s">
         <v>16</v>
@@ -3716,22 +3708,22 @@
         <v>79</v>
       </c>
       <c r="C88" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F88">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G88">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="H88" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I88" t="s">
         <v>16</v>
@@ -3740,7 +3732,7 @@
         <v>17</v>
       </c>
       <c r="K88" s="2">
-        <v>46286.79525653935</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -3751,7 +3743,7 @@
         <v>79</v>
       </c>
       <c r="C89" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D89" t="s">
         <v>27</v>
@@ -3760,13 +3752,13 @@
         <v>28</v>
       </c>
       <c r="F89">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="G89">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="H89" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I89" t="s">
         <v>16</v>
@@ -3786,7 +3778,7 @@
         <v>79</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
         <v>27</v>
@@ -3795,16 +3787,16 @@
         <v>28</v>
       </c>
       <c r="F90">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G90">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J90" t="s">
         <v>17</v>
@@ -3821,7 +3813,7 @@
         <v>79</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D91" t="s">
         <v>27</v>
@@ -3830,7 +3822,7 @@
         <v>28</v>
       </c>
       <c r="F91">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -3856,25 +3848,25 @@
         <v>79</v>
       </c>
       <c r="C92" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E92" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F92">
-        <v>100000</v>
+        <v>25</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H92" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I92" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J92" t="s">
         <v>17</v>
@@ -3891,7 +3883,7 @@
         <v>79</v>
       </c>
       <c r="C93" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D93" t="s">
         <v>13</v>
@@ -3900,13 +3892,13 @@
         <v>14</v>
       </c>
       <c r="F93">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G93">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H93" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I93" t="s">
         <v>16</v>
@@ -3926,22 +3918,22 @@
         <v>79</v>
       </c>
       <c r="C94" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D94" t="s">
         <v>13</v>
       </c>
       <c r="E94" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F94">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G94">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="H94" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I94" t="s">
         <v>16</v>
@@ -3961,7 +3953,7 @@
         <v>79</v>
       </c>
       <c r="C95" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
@@ -3970,13 +3962,13 @@
         <v>21</v>
       </c>
       <c r="F95">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="G95">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="H95" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I95" t="s">
         <v>16</v>
@@ -3985,41 +3977,6 @@
         <v>17</v>
       </c>
       <c r="K95" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>2026</v>
-      </c>
-      <c r="B96" t="s">
-        <v>79</v>
-      </c>
-      <c r="C96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D96" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" t="s">
-        <v>21</v>
-      </c>
-      <c r="F96">
-        <v>70</v>
-      </c>
-      <c r="G96">
-        <v>68</v>
-      </c>
-      <c r="H96" t="s">
-        <v>86</v>
-      </c>
-      <c r="I96" t="s">
-        <v>16</v>
-      </c>
-      <c r="J96" t="s">
-        <v>17</v>
-      </c>
-      <c r="K96" s="2">
         <v>46287.5689004245</v>
       </c>
     </row>

--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/08 Agosto/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/09 Septiembre/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02448D08-70F2-464B-8717-BC1FFDD0993E}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B844F86-2FCA-4326-9F9D-0617811E65DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$79</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="86">
   <si>
     <t>Año</t>
   </si>
@@ -269,9 +285,6 @@
   </si>
   <si>
     <t>138.0%</t>
-  </si>
-  <si>
-    <t>136.0%</t>
   </si>
   <si>
     <t>93.3%</t>
@@ -648,9 +661,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -3157,13 +3172,13 @@
         <v>28</v>
       </c>
       <c r="F72">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="G72">
         <v>42</v>
       </c>
       <c r="H72" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="I72" t="s">
         <v>16</v>
@@ -3172,7 +3187,7 @@
         <v>17</v>
       </c>
       <c r="K72" s="2">
-        <v>46286.795092314816</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3207,7 +3222,7 @@
         <v>17</v>
       </c>
       <c r="K73" s="2">
-        <v>46286.795092314816</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -3242,7 +3257,7 @@
         <v>17</v>
       </c>
       <c r="K74" s="2">
-        <v>46286.795092314816</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -3277,7 +3292,7 @@
         <v>17</v>
       </c>
       <c r="K75" s="2">
-        <v>46286.795092314816</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -3312,7 +3327,7 @@
         <v>17</v>
       </c>
       <c r="K76" s="2">
-        <v>46286.795092314816</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -3347,7 +3362,7 @@
         <v>17</v>
       </c>
       <c r="K77" s="2">
-        <v>46286.795092314816</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -3367,13 +3382,13 @@
         <v>21</v>
       </c>
       <c r="F78">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G78">
         <v>16</v>
       </c>
       <c r="H78" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="I78" t="s">
         <v>16</v>
@@ -3382,7 +3397,7 @@
         <v>17</v>
       </c>
       <c r="K78" s="2">
-        <v>46286.795092314816</v>
+        <v>46287.5689004245</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -3402,13 +3417,13 @@
         <v>21</v>
       </c>
       <c r="F79">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G79">
         <v>68</v>
       </c>
       <c r="H79" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I79" t="s">
         <v>16</v>
@@ -3417,570 +3432,11 @@
         <v>17</v>
       </c>
       <c r="K79" s="2">
-        <v>46286.795092314816</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>2026</v>
-      </c>
-      <c r="B80" t="s">
-        <v>79</v>
-      </c>
-      <c r="C80" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" t="s">
-        <v>27</v>
-      </c>
-      <c r="E80" t="s">
-        <v>28</v>
-      </c>
-      <c r="F80">
-        <v>75</v>
-      </c>
-      <c r="G80">
-        <v>42</v>
-      </c>
-      <c r="H80" t="s">
-        <v>51</v>
-      </c>
-      <c r="I80" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" t="s">
-        <v>17</v>
-      </c>
-      <c r="K80" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>2026</v>
-      </c>
-      <c r="B81" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" t="s">
-        <v>23</v>
-      </c>
-      <c r="D81" t="s">
-        <v>27</v>
-      </c>
-      <c r="E81" t="s">
-        <v>28</v>
-      </c>
-      <c r="F81">
-        <v>150</v>
-      </c>
-      <c r="G81">
-        <v>141</v>
-      </c>
-      <c r="H81" t="s">
-        <v>80</v>
-      </c>
-      <c r="I81" t="s">
-        <v>16</v>
-      </c>
-      <c r="J81" t="s">
-        <v>17</v>
-      </c>
-      <c r="K81" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>2026</v>
-      </c>
-      <c r="B82" t="s">
-        <v>79</v>
-      </c>
-      <c r="C82" t="s">
-        <v>32</v>
-      </c>
-      <c r="D82" t="s">
-        <v>27</v>
-      </c>
-      <c r="E82" t="s">
-        <v>28</v>
-      </c>
-      <c r="F82">
-        <v>60</v>
-      </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82" t="s">
-        <v>20</v>
-      </c>
-      <c r="I82" t="s">
-        <v>20</v>
-      </c>
-      <c r="J82" t="s">
-        <v>17</v>
-      </c>
-      <c r="K82" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>2026</v>
-      </c>
-      <c r="B83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83" t="s">
-        <v>34</v>
-      </c>
-      <c r="D83" t="s">
-        <v>27</v>
-      </c>
-      <c r="E83" t="s">
-        <v>28</v>
-      </c>
-      <c r="F83">
-        <v>100000</v>
-      </c>
-      <c r="G83">
-        <v>0</v>
-      </c>
-      <c r="H83" t="s">
-        <v>20</v>
-      </c>
-      <c r="I83" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" t="s">
-        <v>17</v>
-      </c>
-      <c r="K83" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>2026</v>
-      </c>
-      <c r="B84" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" t="s">
-        <v>12</v>
-      </c>
-      <c r="D84" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" t="s">
-        <v>14</v>
-      </c>
-      <c r="F84">
-        <v>25</v>
-      </c>
-      <c r="G84">
-        <v>23</v>
-      </c>
-      <c r="H84" t="s">
-        <v>81</v>
-      </c>
-      <c r="I84" t="s">
-        <v>16</v>
-      </c>
-      <c r="J84" t="s">
-        <v>17</v>
-      </c>
-      <c r="K84" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>2026</v>
-      </c>
-      <c r="B85" t="s">
-        <v>79</v>
-      </c>
-      <c r="C85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D85" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" t="s">
-        <v>14</v>
-      </c>
-      <c r="F85">
-        <v>50</v>
-      </c>
-      <c r="G85">
-        <v>69</v>
-      </c>
-      <c r="H85" t="s">
-        <v>82</v>
-      </c>
-      <c r="I85" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" t="s">
-        <v>17</v>
-      </c>
-      <c r="K85" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>2026</v>
-      </c>
-      <c r="B86" t="s">
-        <v>79</v>
-      </c>
-      <c r="C86" t="s">
-        <v>12</v>
-      </c>
-      <c r="D86" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" t="s">
-        <v>21</v>
-      </c>
-      <c r="F86">
-        <v>25</v>
-      </c>
-      <c r="G86">
-        <v>16</v>
-      </c>
-      <c r="H86" t="s">
-        <v>56</v>
-      </c>
-      <c r="I86" t="s">
-        <v>16</v>
-      </c>
-      <c r="J86" t="s">
-        <v>17</v>
-      </c>
-      <c r="K86" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>2026</v>
-      </c>
-      <c r="B87" t="s">
-        <v>79</v>
-      </c>
-      <c r="C87" t="s">
-        <v>23</v>
-      </c>
-      <c r="D87" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" t="s">
-        <v>21</v>
-      </c>
-      <c r="F87">
-        <v>50</v>
-      </c>
-      <c r="G87">
-        <v>68</v>
-      </c>
-      <c r="H87" t="s">
-        <v>83</v>
-      </c>
-      <c r="I87" t="s">
-        <v>16</v>
-      </c>
-      <c r="J87" t="s">
-        <v>17</v>
-      </c>
-      <c r="K87" s="2">
-        <v>46286.79525653935</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>2026</v>
-      </c>
-      <c r="B88" t="s">
-        <v>79</v>
-      </c>
-      <c r="C88" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" t="s">
-        <v>27</v>
-      </c>
-      <c r="E88" t="s">
-        <v>28</v>
-      </c>
-      <c r="F88">
-        <v>45</v>
-      </c>
-      <c r="G88">
-        <v>42</v>
-      </c>
-      <c r="H88" t="s">
-        <v>84</v>
-      </c>
-      <c r="I88" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" t="s">
-        <v>17</v>
-      </c>
-      <c r="K88" s="2">
         <v>46287.5689004245</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>2026</v>
-      </c>
-      <c r="B89" t="s">
-        <v>79</v>
-      </c>
-      <c r="C89" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" t="s">
-        <v>27</v>
-      </c>
-      <c r="E89" t="s">
-        <v>28</v>
-      </c>
-      <c r="F89">
-        <v>150</v>
-      </c>
-      <c r="G89">
-        <v>141</v>
-      </c>
-      <c r="H89" t="s">
-        <v>80</v>
-      </c>
-      <c r="I89" t="s">
-        <v>16</v>
-      </c>
-      <c r="J89" t="s">
-        <v>17</v>
-      </c>
-      <c r="K89" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>2026</v>
-      </c>
-      <c r="B90" t="s">
-        <v>79</v>
-      </c>
-      <c r="C90" t="s">
-        <v>32</v>
-      </c>
-      <c r="D90" t="s">
-        <v>27</v>
-      </c>
-      <c r="E90" t="s">
-        <v>28</v>
-      </c>
-      <c r="F90">
-        <v>60</v>
-      </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
-      <c r="H90" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" t="s">
-        <v>20</v>
-      </c>
-      <c r="J90" t="s">
-        <v>17</v>
-      </c>
-      <c r="K90" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>2026</v>
-      </c>
-      <c r="B91" t="s">
-        <v>79</v>
-      </c>
-      <c r="C91" t="s">
-        <v>34</v>
-      </c>
-      <c r="D91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E91" t="s">
-        <v>28</v>
-      </c>
-      <c r="F91">
-        <v>100000</v>
-      </c>
-      <c r="G91">
-        <v>0</v>
-      </c>
-      <c r="H91" t="s">
-        <v>20</v>
-      </c>
-      <c r="I91" t="s">
-        <v>20</v>
-      </c>
-      <c r="J91" t="s">
-        <v>17</v>
-      </c>
-      <c r="K91" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>2026</v>
-      </c>
-      <c r="B92" t="s">
-        <v>79</v>
-      </c>
-      <c r="C92" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92">
-        <v>25</v>
-      </c>
-      <c r="G92">
-        <v>23</v>
-      </c>
-      <c r="H92" t="s">
-        <v>81</v>
-      </c>
-      <c r="I92" t="s">
-        <v>16</v>
-      </c>
-      <c r="J92" t="s">
-        <v>17</v>
-      </c>
-      <c r="K92" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>2026</v>
-      </c>
-      <c r="B93" t="s">
-        <v>79</v>
-      </c>
-      <c r="C93" t="s">
-        <v>23</v>
-      </c>
-      <c r="D93" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" t="s">
-        <v>14</v>
-      </c>
-      <c r="F93">
-        <v>50</v>
-      </c>
-      <c r="G93">
-        <v>69</v>
-      </c>
-      <c r="H93" t="s">
-        <v>82</v>
-      </c>
-      <c r="I93" t="s">
-        <v>16</v>
-      </c>
-      <c r="J93" t="s">
-        <v>17</v>
-      </c>
-      <c r="K93" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>2026</v>
-      </c>
-      <c r="B94" t="s">
-        <v>79</v>
-      </c>
-      <c r="C94" t="s">
-        <v>12</v>
-      </c>
-      <c r="D94" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s">
-        <v>21</v>
-      </c>
-      <c r="F94">
-        <v>15</v>
-      </c>
-      <c r="G94">
-        <v>16</v>
-      </c>
-      <c r="H94" t="s">
-        <v>85</v>
-      </c>
-      <c r="I94" t="s">
-        <v>16</v>
-      </c>
-      <c r="J94" t="s">
-        <v>17</v>
-      </c>
-      <c r="K94" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>2026</v>
-      </c>
-      <c r="B95" t="s">
-        <v>79</v>
-      </c>
-      <c r="C95" t="s">
-        <v>23</v>
-      </c>
-      <c r="D95" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" t="s">
-        <v>21</v>
-      </c>
-      <c r="F95">
-        <v>70</v>
-      </c>
-      <c r="G95">
-        <v>68</v>
-      </c>
-      <c r="H95" t="s">
-        <v>86</v>
-      </c>
-      <c r="I95" t="s">
-        <v>16</v>
-      </c>
-      <c r="J95" t="s">
-        <v>17</v>
-      </c>
-      <c r="K95" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:K79" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/09 Septiembre/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B844F86-2FCA-4326-9F9D-0617811E65DD}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C84993E8-FBC4-4012-B2A2-C509D93D1FE9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="91">
   <si>
     <t>Año</t>
   </si>
@@ -294,6 +294,21 @@
   </si>
   <si>
     <t>97.1%</t>
+  </si>
+  <si>
+    <t>Septiembre</t>
+  </si>
+  <si>
+    <t>102.2%</t>
+  </si>
+  <si>
+    <t>104.7%</t>
+  </si>
+  <si>
+    <t>132.0%</t>
+  </si>
+  <si>
+    <t>131.4%</t>
   </si>
 </sst>
 </file>
@@ -661,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -3187,7 +3202,7 @@
         <v>17</v>
       </c>
       <c r="K72" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3222,7 +3237,7 @@
         <v>17</v>
       </c>
       <c r="K73" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -3257,7 +3272,7 @@
         <v>17</v>
       </c>
       <c r="K74" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -3292,7 +3307,7 @@
         <v>17</v>
       </c>
       <c r="K75" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -3327,7 +3342,7 @@
         <v>17</v>
       </c>
       <c r="K76" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -3362,7 +3377,7 @@
         <v>17</v>
       </c>
       <c r="K77" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -3397,7 +3412,7 @@
         <v>17</v>
       </c>
       <c r="K78" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -3432,11 +3447,291 @@
         <v>17</v>
       </c>
       <c r="K79" s="2">
-        <v>46287.5689004245</v>
+        <v>46287.568900428239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2026</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80">
+        <v>45</v>
+      </c>
+      <c r="G80">
+        <v>46</v>
+      </c>
+      <c r="H80" t="s">
+        <v>87</v>
+      </c>
+      <c r="I80" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80" s="2">
+        <v>46318.759673496243</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2026</v>
+      </c>
+      <c r="B81" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81">
+        <v>150</v>
+      </c>
+      <c r="G81">
+        <v>157</v>
+      </c>
+      <c r="H81" t="s">
+        <v>88</v>
+      </c>
+      <c r="I81" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="2">
+        <v>46318.759673496243</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82">
+        <v>60</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82" s="2">
+        <v>46318.759673496243</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2026</v>
+      </c>
+      <c r="B83" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83">
+        <v>100000</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="2">
+        <v>46318.759673496243</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2026</v>
+      </c>
+      <c r="B84" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84">
+        <v>25</v>
+      </c>
+      <c r="G84">
+        <v>28</v>
+      </c>
+      <c r="H84" t="s">
+        <v>70</v>
+      </c>
+      <c r="I84" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" s="2">
+        <v>46318.759673496243</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2026</v>
+      </c>
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85">
+        <v>50</v>
+      </c>
+      <c r="G85">
+        <v>66</v>
+      </c>
+      <c r="H85" t="s">
+        <v>89</v>
+      </c>
+      <c r="I85" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85" s="2">
+        <v>46318.759673496243</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2026</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>21</v>
+      </c>
+      <c r="F86">
+        <v>15</v>
+      </c>
+      <c r="G86">
+        <v>16</v>
+      </c>
+      <c r="H86" t="s">
+        <v>84</v>
+      </c>
+      <c r="I86" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" s="2">
+        <v>46318.759673496243</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2026</v>
+      </c>
+      <c r="B87" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87">
+        <v>70</v>
+      </c>
+      <c r="G87">
+        <v>92</v>
+      </c>
+      <c r="H87" t="s">
+        <v>90</v>
+      </c>
+      <c r="I87" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="2">
+        <v>46318.759673496243</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K79" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K78" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>